--- a/Final_Regressions/Inbreeding_FEBA/inbreeding_at_FEBA.xlsx
+++ b/Final_Regressions/Inbreeding_FEBA/inbreeding_at_FEBA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stoycho.rusinov\Desktop\inbreeding\Regressions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stoycho.rusinov\Documents\GitHub\Academic_inbreeding_research\Final_Regressions\Inbreeding_FEBA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49468B78-471F-4CB8-B186-0B952DA52E9F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125C10D6-606D-4966-9470-542349F54241}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9804" tabRatio="785" xr2:uid="{C6FBF984-0647-43F8-9E0B-FC7BC60D6D1A}"/>
   </bookViews>
